--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_魔法书配置表_Manufacture_MagicBookConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_魔法书配置表_Manufacture_MagicBookConfig.xlsx
@@ -1,40 +1,518 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+  <si>
+    <t>魔法书ID</t>
+  </si>
+  <si>
+    <t>是否唯一</t>
+  </si>
+  <si>
+    <t>生效环节</t>
+  </si>
+  <si>
+    <t>魔法书效果</t>
+  </si>
+  <si>
+    <t>魔法书效果参数</t>
+  </si>
+  <si>
+    <t>魔法书Icon</t>
+  </si>
+  <si>
+    <t>魔法书名称</t>
+  </si>
+  <si>
+    <t>魔法书介绍</t>
+  </si>
+  <si>
+    <t>主键</t>
+  </si>
+  <si>
+    <t>1=同 Id 不可叠装第二本；0=默认可叠（各占一槽）</t>
+  </si>
+  <si>
+    <t>Phase 或 Phase|Phase|…；至少 SoldierManufacture / Combat</t>
+  </si>
+  <si>
+    <t>已登记 PascalCase Token；空=无效果；禁止中文或内联参数</t>
+  </si>
+  <si>
+    <t>Key=Value 或 Key=Value|…；空=无参/缺省</t>
+  </si>
+  <si>
+    <t>UI 图标资源 Id</t>
+  </si>
+  <si>
+    <t>展示名；若启用 i18n 可为 Key</t>
+  </si>
+  <si>
+    <t>展示文案</t>
+  </si>
+  <si>
+    <t>MagicBookId</t>
+  </si>
+  <si>
+    <t>IsUnique</t>
+  </si>
+  <si>
+    <t>EffectPhase</t>
+  </si>
+  <si>
+    <t>EffectPayload</t>
+  </si>
+  <si>
+    <t>EffectParams</t>
+  </si>
+  <si>
+    <t>IconAssetId</t>
+  </si>
+  <si>
+    <t>DisplayName</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>MagicBook_Restore</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>SoldierManufacture</t>
+  </si>
+  <si>
+    <t>RaceWeightPick</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>还原</t>
+  </si>
+  <si>
+    <t>装备后制造时按部位 RaceId 加权随机定种族</t>
+  </si>
+  <si>
+    <t>MagicBook_WarriorEnhance</t>
+  </si>
+  <si>
+    <t>StatMul</t>
+  </si>
+  <si>
+    <t>Stat=Primary|Mul=1.15|ClassId=Class_Warrior</t>
+  </si>
+  <si>
+    <t>鎴樺＋寮哄寲</t>
+  </si>
+  <si>
+    <t>瑁呭鍚庯紝Mode2 鍒堕€犵殑鎴樺＋涓诲睘鎬у鍔犺函浣撹缁翠箣鍜岀殑 15%锛堝彲鍙狅級锛岃嚦褰诲簳姝讳骸</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
+  <fills count="34">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -42,85 +520,313 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -403,131 +1109,144 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="7"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>魔法书ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>是否唯一</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>生效环节</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>魔法书效果</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>魔法书Icon</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>魔法书名称</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>魔法书介绍</t>
-        </is>
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1=同 Id 不可叠装第二本；0=默认可叠</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SoldierManufacture|Combat|…</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>本轮占位串；空=无效果</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>UI 图标资源 Id</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>展示名或本地化 Key</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>展示文案</t>
-        </is>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>MagicBookId</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IsUnique</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>EffectPhase</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>EffectPayload</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>IconAssetId</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>DisplayName</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
+    <row r="3" s="1" customFormat="1" spans="1:8">
+      <c r="A3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_魔法书配置表_Manufacture_MagicBookConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_魔法书配置表_Manufacture_MagicBookConfig.xlsx
@@ -214,7 +214,7 @@
     <t>ClassId=Class_Rogue|RequireClassId=Class_Rogue_0|Chance=0.25</t>
   </si>
   <si>
-    <t>盗贼进阶</t>
+    <t>刺客进阶</t>
   </si>
   <si>
     <t>装备后，Mode2 制造职业为 Class_Rogue_0 的士兵时，25% 概率变为 Class_Rogue</t>
@@ -230,14 +230,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -699,148 +692,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_魔法书配置表_Manufacture_MagicBookConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_魔法书配置表_Manufacture_MagicBookConfig.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\CursorGame_Git\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12280"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="77">
   <si>
     <t>魔法书ID</t>
   </si>
@@ -61,6 +61,15 @@
     <t>魔法书介绍</t>
   </si>
   <si>
+    <t>特效外观ID</t>
+  </si>
+  <si>
+    <t>特效优先级</t>
+  </si>
+  <si>
+    <t>特效强度加算</t>
+  </si>
+  <si>
     <t>主键</t>
   </si>
   <si>
@@ -88,6 +97,15 @@
     <t>展示文案</t>
   </si>
   <si>
+    <t>空=无特效；Catalog StyleId；非 Token；仅命中才竞争</t>
+  </si>
+  <si>
+    <t>缺/空=0。更高覆盖并重置 Intensity；同 StyleId 累加；更低忽略</t>
+  </si>
+  <si>
+    <t>缺/空=1。覆盖时写入；同 style 累加</t>
+  </si>
+  <si>
     <t>MagicBookId</t>
   </si>
   <si>
@@ -115,6 +133,15 @@
     <t>Description</t>
   </si>
   <si>
+    <t>VisualStyleId</t>
+  </si>
+  <si>
+    <t>VisualPriority</t>
+  </si>
+  <si>
+    <t>VisualIntensityAdd</t>
+  </si>
+  <si>
     <t>MagicBook_Restore</t>
   </si>
   <si>
@@ -145,13 +172,19 @@
     <t>StatMul</t>
   </si>
   <si>
-    <t>Stat=Primary|Mul=1.15|ClassId=Class_Warrior</t>
+    <t>Stat=Primary|Mul=1.15|ClassId=Class_BaseWarrior,Class_Warrior</t>
   </si>
   <si>
     <t>战士强化</t>
   </si>
   <si>
-    <t>装备后，Mode2 制造的战士主属性增加躯体该维之和的 15%（可叠），至彻底死亡</t>
+    <t>装备后，Mode2 制造的枯骨战士/战士主属性增加躯体该维之和的 15%（可叠），至彻底死亡</t>
+  </si>
+  <si>
+    <t>Style_WarriorGlow</t>
+  </si>
+  <si>
+    <t>20</t>
   </si>
   <si>
     <t>MagicBook_SoldierSkillLevel</t>
@@ -169,55 +202,67 @@
     <t>装备后，Mode2 制造时若士兵已有 Skill_01 则等级 +1（钳制到表内最大级）</t>
   </si>
   <si>
+    <t>Style_SkillAberration</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>MagicBook_WarriorAdvance</t>
   </si>
   <si>
     <t>ForceClass</t>
   </si>
   <si>
-    <t>ClassId=Class_Warrior|RequireClassId=Class_Warrior_0|Chance=1</t>
+    <t>ClassId=Class_Warrior|RequireClassId=Class_BaseWarrior|Chance=1</t>
   </si>
   <si>
     <t>战士进阶</t>
   </si>
   <si>
-    <t>装备后，Mode2 制造职业为 Class_Warrior_0 的士兵时，25% 概率变为 Class_Warrior</t>
+    <t>装备后，Mode2 制造职业为 Class_BaseWarrior 的士兵时，变为 Class_Warrior</t>
+  </si>
+  <si>
+    <t>Style_AdvanceOutline</t>
+  </si>
+  <si>
+    <t>30</t>
   </si>
   <si>
     <t>MagicBook_ArcherAdvance</t>
   </si>
   <si>
-    <t>ClassId=Class_Archer|RequireClassId=Class_Archer_0|Chance=0.25</t>
+    <t>ClassId=Class_Archer|RequireClassId=Class_BaseArcher|Chance=0.25</t>
   </si>
   <si>
     <t>射手进阶</t>
   </si>
   <si>
-    <t>装备后，Mode2 制造职业为 Class_Archer_0 的士兵时，25% 概率变为 Class_Archer</t>
+    <t>装备后，Mode2 制造职业为 Class_BaseArcher 的士兵时，25% 概率变为 Class_Archer</t>
   </si>
   <si>
     <t>MagicBook_MageAdvance</t>
   </si>
   <si>
-    <t>ClassId=Class_Mage|RequireClassId=Class_Mage_0|Chance=0.25</t>
+    <t>ClassId=Class_Mage|RequireClassId=Class_BaseMage|Chance=0.25</t>
   </si>
   <si>
     <t>法师进阶</t>
   </si>
   <si>
-    <t>装备后，Mode2 制造职业为 Class_Mage_0 的士兵时，25% 概率变为 Class_Mage</t>
+    <t>装备后，Mode2 制造职业为 Class_BaseMage 的士兵时，25% 概率变为 Class_Mage</t>
   </si>
   <si>
     <t>MagicBook_RogueAdvance</t>
   </si>
   <si>
-    <t>ClassId=Class_Rogue|RequireClassId=Class_Rogue_0|Chance=0.25</t>
+    <t>ClassId=Class_Rogue|RequireClassId=Class_BaseRogue|Chance=0.25</t>
   </si>
   <si>
     <t>刺客进阶</t>
   </si>
   <si>
-    <t>装备后，Mode2 制造职业为 Class_Rogue_0 的士兵时，25% 概率变为 Class_Rogue</t>
+    <t>装备后，Mode2 制造职业为 Class_BaseRogue 的士兵时，25% 概率变为 Class_Rogue</t>
   </si>
 </sst>
 </file>
@@ -837,9 +882,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1186,10 +1234,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:L10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <cols>
+    <col min="9" max="9" width="29.6363636363636" customWidth="1"/>
+    <col min="10" max="10" width="23.6363636363636" customWidth="1"/>
+    <col min="11" max="11" width="16.6363636363636" customWidth="1"/>
+    <col min="12" max="12" width="21.5454545454545" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1217,266 +1271,349 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="J2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:9">
+    <row r="3" s="1" customFormat="1" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="H4" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="I4" t="s">
-        <v>34</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="F5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5" t="s">
+        <v>49</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5" t="s">
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" t="s">
         <v>38</v>
       </c>
-      <c r="I5" t="s">
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
         <v>39</v>
       </c>
+      <c r="E6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" t="s">
+        <v>54</v>
+      </c>
+      <c r="I6" t="s">
+        <v>55</v>
+      </c>
+      <c r="J6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" t="s">
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G7" t="s">
         <v>41</v>
       </c>
-      <c r="F6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" t="s">
-        <v>43</v>
-      </c>
-      <c r="I6" t="s">
-        <v>44</v>
+      <c r="H7" t="s">
+        <v>61</v>
+      </c>
+      <c r="I7" t="s">
+        <v>62</v>
+      </c>
+      <c r="J7" t="s">
+        <v>63</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" t="s">
-        <v>49</v>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" t="s">
+        <v>66</v>
+      </c>
+      <c r="G8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I8" t="s">
+        <v>68</v>
+      </c>
+      <c r="J8" t="s">
+        <v>63</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I8" t="s">
-        <v>53</v>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" t="s">
+        <v>70</v>
+      </c>
+      <c r="G9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I9" t="s">
+        <v>72</v>
+      </c>
+      <c r="J9" t="s">
+        <v>63</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>54</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" t="s">
-        <v>46</v>
-      </c>
-      <c r="F9" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H9" t="s">
-        <v>56</v>
-      </c>
-      <c r="I9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E10" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="G10" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="H10" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="I10" t="s">
-        <v>61</v>
+        <v>76</v>
+      </c>
+      <c r="J10" t="s">
+        <v>63</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_魔法书配置表_Manufacture_MagicBookConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_魔法书配置表_Manufacture_MagicBookConfig.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\CursorGame_Git\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12280"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="74">
   <si>
     <t>魔法书ID</t>
   </si>
@@ -181,10 +181,7 @@
     <t>装备后，Mode2 制造的枯骨战士/战士主属性增加躯体该维之和的 15%（可叠），至彻底死亡</t>
   </si>
   <si>
-    <t>Style_WarriorGlow</t>
-  </si>
-  <si>
-    <t>20</t>
+    <t>Style_ScaleModel</t>
   </si>
   <si>
     <t>MagicBook_SoldierSkillLevel</t>
@@ -221,12 +218,6 @@
   </si>
   <si>
     <t>装备后，Mode2 制造职业为 Class_BaseWarrior 的士兵时，变为 Class_Warrior</t>
-  </si>
-  <si>
-    <t>Style_AdvanceOutline</t>
-  </si>
-  <si>
-    <t>30</t>
   </si>
   <si>
     <t>MagicBook_ArcherAdvance</t>
@@ -737,148 +728,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1235,12 +1226,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="9" max="9" width="29.6363636363636" customWidth="1"/>
-    <col min="10" max="10" width="23.6363636363636" customWidth="1"/>
-    <col min="11" max="11" width="16.6363636363636" customWidth="1"/>
-    <col min="12" max="12" width="21.5454545454545" customWidth="1"/>
+    <col min="8" max="8" width="16.75" customWidth="1"/>
+    <col min="9" max="9" width="29.6333333333333" customWidth="1"/>
+    <col min="10" max="10" width="23.6333333333333" customWidth="1"/>
+    <col min="11" max="11" width="16.6333333333333" customWidth="1"/>
+    <col min="12" max="12" width="21.5416666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -1385,8 +1377,6 @@
       <c r="I4" t="s">
         <v>43</v>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
@@ -1419,16 +1409,16 @@
       <c r="J5" t="s">
         <v>49</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>37</v>
+      <c r="K5" s="2">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2">
+        <v>1.5</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s">
         <v>38</v>
@@ -1440,25 +1430,25 @@
         <v>39</v>
       </c>
       <c r="E6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" t="s">
         <v>52</v>
-      </c>
-      <c r="F6" t="s">
-        <v>53</v>
       </c>
       <c r="G6" t="s">
         <v>41</v>
       </c>
       <c r="H6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I6" t="s">
         <v>54</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>55</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>37</v>
@@ -1466,7 +1456,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s">
         <v>37</v>
@@ -1478,33 +1468,26 @@
         <v>39</v>
       </c>
       <c r="E7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="G7" t="s">
         <v>41</v>
       </c>
       <c r="H7" t="s">
+        <v>60</v>
+      </c>
+      <c r="I7" t="s">
         <v>61</v>
       </c>
-      <c r="I7" t="s">
-        <v>62</v>
-      </c>
-      <c r="J7" t="s">
-        <v>63</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B8" t="s">
         <v>37</v>
@@ -1516,33 +1499,26 @@
         <v>39</v>
       </c>
       <c r="E8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F8" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G8" t="s">
         <v>41</v>
       </c>
       <c r="H8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I8" t="s">
-        <v>68</v>
-      </c>
-      <c r="J8" t="s">
-        <v>63</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B9" t="s">
         <v>37</v>
@@ -1554,33 +1530,26 @@
         <v>39</v>
       </c>
       <c r="E9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G9" t="s">
         <v>41</v>
       </c>
       <c r="H9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I9" t="s">
-        <v>72</v>
-      </c>
-      <c r="J9" t="s">
-        <v>63</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B10" t="s">
         <v>37</v>
@@ -1592,29 +1561,22 @@
         <v>39</v>
       </c>
       <c r="E10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F10" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G10" t="s">
         <v>41</v>
       </c>
       <c r="H10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I10" t="s">
-        <v>76</v>
-      </c>
-      <c r="J10" t="s">
-        <v>63</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_魔法书配置表_Manufacture_MagicBookConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_魔法书配置表_Manufacture_MagicBookConfig.xlsx
@@ -1228,6 +1228,8 @@
   <dimension ref="A1:L10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
+    <col min="1" max="1" width="17.5" customWidth="1"/>
+    <col min="7" max="7" width="22.625" customWidth="1"/>
     <col min="8" max="8" width="16.75" customWidth="1"/>
     <col min="9" max="9" width="29.6333333333333" customWidth="1"/>
     <col min="10" max="10" width="23.6333333333333" customWidth="1"/>
@@ -1369,7 +1371,7 @@
         <v>41</v>
       </c>
       <c r="G4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="H4" t="s">
         <v>42</v>
@@ -1398,7 +1400,7 @@
         <v>46</v>
       </c>
       <c r="G5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H5" t="s">
         <v>47</v>
@@ -1436,7 +1438,7 @@
         <v>52</v>
       </c>
       <c r="G6" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="H6" t="s">
         <v>53</v>
@@ -1474,7 +1476,7 @@
         <v>59</v>
       </c>
       <c r="G7" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="H7" t="s">
         <v>60</v>
@@ -1505,7 +1507,7 @@
         <v>63</v>
       </c>
       <c r="G8" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="H8" t="s">
         <v>64</v>
@@ -1536,7 +1538,7 @@
         <v>67</v>
       </c>
       <c r="G9" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="H9" t="s">
         <v>68</v>
@@ -1567,7 +1569,7 @@
         <v>71</v>
       </c>
       <c r="G10" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="H10" t="s">
         <v>72</v>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_魔法书配置表_Manufacture_MagicBookConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/制造_魔法书配置表_Manufacture_MagicBookConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,7 +489,6 @@
           <t>1=同 Id 不可叠装第二本；0=默认可叠（各占一槽）</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>Phase 或 Phase|Phase|…；至少 SoldierManufacture / Combat</t>
@@ -520,9 +519,6 @@
           <t>展示文案</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -612,7 +608,6 @@
           <t>RaceWeightPick</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>MagicBook_Restore</t>
@@ -628,9 +623,6 @@
           <t>装备后制造时按部位 RaceId 加权随机定种族</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -802,9 +794,6 @@
           <t>装备后，Mode2 制造职业为 Class_BaseWarrior 的士兵时，变为 Class_Warrior</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -852,9 +841,6 @@
           <t>装备后，Mode2 制造职业为 Class_BaseArcher 的士兵时，25% 概率变为 Class_Archer</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -902,9 +888,6 @@
           <t>装备后，Mode2 制造职业为 Class_BaseMage 的士兵时，25% 概率变为 Class_Mage</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -952,9 +935,6 @@
           <t>装备后，Mode2 制造职业为 Class_BaseRogue 的士兵时，25% 概率变为 Class_Rogue</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1002,9 +982,6 @@
           <t>装备后，战斗时上阵士兵生命上限提升 15%（开战生效，不改制造 Base）</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1052,9 +1029,6 @@
           <t>装备后，战斗时上阵士兵生命上限提升 30%（开战生效，不改制造 Base）</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1102,9 +1076,6 @@
           <t>装备后，战斗时上阵士兵力量提升 15%（开战生效，不改制造 Base）</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1152,9 +1123,6 @@
           <t>装备后，战斗时上阵士兵力量提升 30%（开战生效，不改制造 Base）</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1202,9 +1170,6 @@
           <t>装备后，战斗时上阵士兵敏捷提升 15%（开战生效，不改制造 Base）</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1252,9 +1217,6 @@
           <t>装备后，战斗时上阵士兵敏捷提升 30%（开战生效，不改制造 Base）</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1302,9 +1264,6 @@
           <t>装备后，战斗时上阵士兵智力提升 15%（开战生效，不改制造 Base）</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1352,9 +1311,95 @@
           <t>装备后，战斗时上阵士兵智力提升 30%（开战生效，不改制造 Base）</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MagicBook_Form_Wedge</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SoldierManufacture</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>GrantFormationSkill</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>FormationId=Form_Wedge_01</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>MagicBook_Form_Wedge</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>楔阵</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>装备后，Mode2 制造 Step2 命中时授予楔阵技能（写入 SoldierSkills）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MagicBook_Form_Wedge_02</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SoldierManufacture</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>GrantFormationSkill</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>FormationId=Form_Wedge_02</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>MagicBook_Form_Wedge_02</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>平行阵</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>装备后，Mode2 制造 Step2 命中时授予平行阵技能（写入 SoldierSkills）</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
